--- a/Report/NFA.xlsx
+++ b/Report/NFA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Compiler Project\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523695EB-8F59-488B-AB17-FCE15080A038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF8F1CB-3CEF-48CF-9DA1-00B335093AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -108,9 +108,6 @@
     <t>)</t>
   </si>
   <si>
-    <t>,</t>
-  </si>
-  <si>
     <t>{</t>
   </si>
   <si>
@@ -433,6 +430,9 @@
   </si>
   <si>
     <t>@</t>
+  </si>
+  <si>
+    <t>Any Character</t>
   </si>
 </sst>
 </file>
@@ -627,11 +627,11 @@
     <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name=";" dataDxfId="7"/>
     <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="(" dataDxfId="6"/>
     <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name=")" dataDxfId="5"/>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="," dataDxfId="4"/>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="{" dataDxfId="3"/>
-    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="}" dataDxfId="2"/>
-    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="#" dataDxfId="1"/>
-    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="#*" dataDxfId="0"/>
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name="{" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{1C25952C-1B19-4601-97CE-1748B1D5AA23}" name="Any Character" dataDxfId="0"/>
+    <tableColumn id="30" xr3:uid="{00000000-0010-0000-0000-00001E000000}" name="}" dataDxfId="3"/>
+    <tableColumn id="31" xr3:uid="{00000000-0010-0000-0000-00001F000000}" name="#" dataDxfId="2"/>
+    <tableColumn id="32" xr3:uid="{00000000-0010-0000-0000-000020000000}" name="#*" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight18" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -918,8 +918,11 @@
     <col min="21" max="23" width="8.88671875"/>
     <col min="24" max="24" width="12" style="1" customWidth="1"/>
     <col min="25" max="25" width="8.88671875"/>
-    <col min="26" max="31" width="12" style="1" customWidth="1"/>
-    <col min="32" max="32" width="34" style="1" customWidth="1"/>
+    <col min="26" max="28" width="12" style="1" customWidth="1"/>
+    <col min="29" max="29" width="17.33203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12" style="1" customWidth="1"/>
+    <col min="31" max="31" width="28.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="30.21875" style="1" bestFit="1" customWidth="1"/>
     <col min="33" max="33" width="33.33203125" style="1" customWidth="1"/>
     <col min="34" max="38" width="12" style="1" customWidth="1"/>
     <col min="39" max="39" width="36" style="1" customWidth="1"/>
@@ -1012,16 +1015,16 @@
         <v>27</v>
       </c>
       <c r="AC1" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="AD1" s="1" t="s">
-        <v>29</v>
-      </c>
       <c r="AE1" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF1" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="AF1" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="AG1"/>
       <c r="AH1"/>
@@ -1034,198 +1037,198 @@
     </row>
     <row r="2" spans="1:40" s="1" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD2" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE2" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF2" s="1" t="s">
         <v>131</v>
-      </c>
-      <c r="AF2" s="1" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE3" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG3"/>
       <c r="AH3"/>
@@ -1238,100 +1241,100 @@
     </row>
     <row r="4" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE4" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="AG4"/>
       <c r="AH4"/>
@@ -1344,100 +1347,100 @@
     </row>
     <row r="5" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE5" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF5" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AG5"/>
       <c r="AH5"/>
@@ -1450,100 +1453,100 @@
     </row>
     <row r="6" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE6" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="AG6"/>
       <c r="AH6"/>
@@ -1556,100 +1559,100 @@
     </row>
     <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE7" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AG7"/>
       <c r="AH7"/>
@@ -1662,100 +1665,100 @@
     </row>
     <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE8" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="AG8"/>
       <c r="AH8"/>
@@ -1768,100 +1771,100 @@
     </row>
     <row r="9" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE9" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AG9"/>
       <c r="AH9"/>
@@ -1874,100 +1877,100 @@
     </row>
     <row r="10" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE10" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AG10"/>
       <c r="AH10"/>
@@ -1980,100 +1983,100 @@
     </row>
     <row r="11" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE11" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="AG11"/>
       <c r="AH11"/>
@@ -2086,100 +2089,100 @@
     </row>
     <row r="12" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE12" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="AG12"/>
       <c r="AH12"/>
@@ -2192,100 +2195,100 @@
     </row>
     <row r="13" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE13" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="AG13"/>
       <c r="AH13"/>
@@ -2298,100 +2301,100 @@
     </row>
     <row r="14" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE14" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="AG14"/>
       <c r="AH14"/>
@@ -2404,100 +2407,100 @@
     </row>
     <row r="15" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE15" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AG15"/>
       <c r="AH15"/>
@@ -2510,100 +2513,100 @@
     </row>
     <row r="16" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE16" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AG16"/>
       <c r="AH16"/>
@@ -2616,100 +2619,100 @@
     </row>
     <row r="17" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE17" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="AG17"/>
       <c r="AH17"/>
@@ -2722,100 +2725,100 @@
     </row>
     <row r="18" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>135</v>
+        <v>45</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>46</v>
+        <v>134</v>
       </c>
       <c r="R18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE18" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="AG18"/>
       <c r="AH18"/>
@@ -2828,100 +2831,100 @@
     </row>
     <row r="19" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE19" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AG19"/>
       <c r="AH19"/>
@@ -2934,100 +2937,100 @@
     </row>
     <row r="20" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE20" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AG20"/>
       <c r="AH20"/>
@@ -3040,100 +3043,100 @@
     </row>
     <row r="21" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE21" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AG21"/>
       <c r="AH21"/>
@@ -3146,100 +3149,100 @@
     </row>
     <row r="22" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE22" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF22" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="AG22"/>
       <c r="AH22"/>
@@ -3252,100 +3255,100 @@
     </row>
     <row r="23" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE23" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="AG23"/>
       <c r="AH23"/>
@@ -3358,100 +3361,100 @@
     </row>
     <row r="24" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="N24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE24" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AG24"/>
       <c r="AH24"/>
@@ -3464,100 +3467,100 @@
     </row>
     <row r="25" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE25" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AG25"/>
       <c r="AH25"/>
@@ -3570,100 +3573,100 @@
     </row>
     <row r="26" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N26" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="O26" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE26" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF26" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AG26"/>
       <c r="AH26"/>
@@ -3676,100 +3679,100 @@
     </row>
     <row r="27" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE27" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="AG27"/>
       <c r="AH27"/>
@@ -3782,100 +3785,100 @@
     </row>
     <row r="28" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O28" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE28" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AG28"/>
       <c r="AH28"/>
@@ -3888,100 +3891,100 @@
     </row>
     <row r="29" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE29" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF29" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="AG29"/>
       <c r="AH29"/>
@@ -3994,100 +3997,100 @@
     </row>
     <row r="30" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE30" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="AG30"/>
       <c r="AH30"/>
@@ -4100,100 +4103,100 @@
     </row>
     <row r="31" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE31" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="AG31"/>
       <c r="AH31"/>
@@ -4206,100 +4209,100 @@
     </row>
     <row r="32" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE32" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="AG32"/>
       <c r="AH32"/>
@@ -4312,100 +4315,100 @@
     </row>
     <row r="33" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="R33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE33" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AG33"/>
       <c r="AH33"/>
@@ -4418,100 +4421,100 @@
     </row>
     <row r="34" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="N34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE34" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="AG34"/>
       <c r="AH34"/>
@@ -4524,100 +4527,100 @@
     </row>
     <row r="35" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE35" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF35" s="1" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="AG35"/>
       <c r="AH35"/>
@@ -4630,100 +4633,100 @@
     </row>
     <row r="36" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE36" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="AG36"/>
       <c r="AH36"/>
@@ -4736,100 +4739,100 @@
     </row>
     <row r="37" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE37" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="AG37"/>
       <c r="AH37"/>
@@ -4842,100 +4845,100 @@
     </row>
     <row r="38" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE38" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG38"/>
       <c r="AH38"/>
@@ -4948,100 +4951,100 @@
     </row>
     <row r="39" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE39" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF39" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="AG39"/>
       <c r="AH39"/>
@@ -5054,100 +5057,100 @@
     </row>
     <row r="40" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE40" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF40" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="AG40"/>
       <c r="AH40"/>
@@ -5160,100 +5163,100 @@
     </row>
     <row r="41" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE41" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF41" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AG41"/>
       <c r="AH41"/>
@@ -5266,100 +5269,100 @@
     </row>
     <row r="42" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE42" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="AG42"/>
       <c r="AH42"/>
@@ -5372,100 +5375,100 @@
     </row>
     <row r="43" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="S43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE43" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF43" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="AG43"/>
       <c r="AH43"/>
@@ -5478,100 +5481,100 @@
     </row>
     <row r="44" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S44" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE44" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="AG44"/>
       <c r="AH44"/>
@@ -5584,100 +5587,100 @@
     </row>
     <row r="45" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE45" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="AG45"/>
       <c r="AH45"/>
@@ -5690,100 +5693,100 @@
     </row>
     <row r="46" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="V46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="W46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="X46" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Y46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE46" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF46" s="1" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AG46"/>
       <c r="AH46"/>
@@ -5796,100 +5799,100 @@
     </row>
     <row r="47" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE47" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF47" s="1" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="AG47"/>
       <c r="AH47"/>
@@ -5902,100 +5905,100 @@
     </row>
     <row r="48" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Z48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AA48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AB48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AC48" s="1" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="AD48" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AE48" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF48" s="1" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AG48"/>
       <c r="AH48"/>
@@ -6008,100 +6011,100 @@
     </row>
     <row r="49" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE49" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF49" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AG49"/>
       <c r="AH49"/>
@@ -6114,100 +6117,100 @@
     </row>
     <row r="50" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB50" s="1" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="AC50" s="1" t="s">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="AD50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE50" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF50" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AG50"/>
       <c r="AH50"/>
@@ -6220,100 +6223,100 @@
     </row>
     <row r="51" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="E51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="F51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="J51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="K51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="L51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="M51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="N51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="O51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="P51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="R51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="S51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="T51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="U51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="V51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="W51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="X51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB51" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC51" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="AD51" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="C51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="F51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="I51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="J51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="L51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="M51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="N51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="O51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="P51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q51" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="R51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="S51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="T51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="U51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="V51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="W51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="X51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="Y51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="Z51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AA51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AC51" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="AD51" s="1" t="s">
-        <v>130</v>
-      </c>
       <c r="AE51" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF51" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="AG51"/>
       <c r="AH51"/>
@@ -6326,100 +6329,100 @@
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="J52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="O52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="P52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Q52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="R52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="S52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="T52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="V52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="W52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="X52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Y52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="Z52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AA52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AB52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AC52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AD52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AE52" s="1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AF52" s="1" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="AG52"/>
       <c r="AH52"/>
